--- a/output/pdf_financials_xlsx/PUL.xlsx
+++ b/output/pdf_financials_xlsx/PUL.xlsx
@@ -2307,10 +2307,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="3" t="n">
+        <v>10.286827</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.102511</v>
@@ -2417,10 +2415,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="3" t="n">
+        <v>10.286827</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.102511</v>
@@ -5579,22 +5575,22 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.081169</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.86131</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.86131</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.86131</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.410425</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.410425</v>
       </c>
     </row>
     <row r="93">
@@ -7004,7 +7000,7 @@
         <v>-0.109277</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001894</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -9540,7 +9536,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11872,7 +11872,11 @@
           <t>Reserves 2,861,310</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13500,7 +13504,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -25212,7 +25220,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -36506,7 +36514,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PUL.xlsx
+++ b/output/pdf_financials_xlsx/PUL.xlsx
@@ -930,13 +930,13 @@
         <v>4.41379</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.469025</v>
+        <v>3.684258</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.496654</v>
+        <v>4.499495</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.49197</v>
+        <v>4.132279</v>
       </c>
     </row>
     <row r="11">
@@ -987,13 +987,13 @@
         <v>1.314197</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2.515651</v>
+        <v>-0.699582</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>4.191233</v>
+        <v>0.188392</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.492969</v>
+        <v>-1.14734</v>
       </c>
     </row>
     <row r="12">
@@ -1026,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00682</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000185</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.07403999999999999</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.08044800000000001</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1957,13 +1957,13 @@
         <v>-0.123061</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.211932</v>
+        <v>-1.218752</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.374279</v>
+        <v>-0.374464</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.10247</v>
+        <v>-3.17651</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-3.176329</v>
@@ -1972,7 +1972,7 @@
         <v>1.009407</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.393876</v>
+        <v>1.313428</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.697515</v>
@@ -2071,13 +2071,13 @@
         <v>-0.123061</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.197851</v>
+        <v>-1.204671</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.347434</v>
+        <v>-0.347619</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.956856</v>
+        <v>-3.030896</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.935141</v>
@@ -2086,7 +2086,7 @@
         <v>1.260586</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.726851</v>
+        <v>1.646403</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.346744</v>
@@ -2128,13 +2128,13 @@
         <v>-1226.684609250399</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-187.9099865089574</v>
+        <v>-188.97985755969</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-13.92971594419518</v>
+        <v>-13.93713317293409</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-142.6130373088473</v>
+        <v>-146.1840834748922</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-303.8964171971225</v>
@@ -2143,7 +2143,7 @@
         <v>40.16514858816628</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>30.14760682941494</v>
+        <v>28.74313436814713</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-45.1219495851476</v>
@@ -2297,10 +2297,10 @@
         <v>0.167459</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.119162</v>
+        <v>0.651224</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.859656</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>10.286827</v>
+        <v>1.286827</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.102511</v>
@@ -2405,10 +2405,10 @@
         <v>0.167459</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.119162</v>
+        <v>0.651224</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.859656</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>10.286827</v>
+        <v>1.286827</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.102511</v>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -42966,7 +42966,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -45326,7 +45326,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -46514,7 +46514,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -46602,7 +46602,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -48830,7 +48830,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -49604,7 +49604,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -50110,7 +50110,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -51134,7 +51134,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
